--- a/output/pdf_financials_xlsx/JBR.xlsx
+++ b/output/pdf_financials_xlsx/JBR.xlsx
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.3723</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.3723</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.3723</v>
       </c>
     </row>
     <row r="93">
@@ -3262,7 +3262,11 @@
           <t>Share based payment reserve (Note 12)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -3709,7 +3713,11 @@
           <t>Share based payment reserve (Note 14)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
         <v>0.3723</v>
       </c>

--- a/output/pdf_financials_xlsx/JBR.xlsx
+++ b/output/pdf_financials_xlsx/JBR.xlsx
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.017765</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.003365</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.020269</v>
       </c>
     </row>
     <row r="35">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.017765</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.003365</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.020269</v>
       </c>
     </row>
     <row r="37">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.37325</v>
+        <v>0.355485</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.025141</v>
+        <v>0.021776</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.027162</v>
+        <v>0.006893</v>
       </c>
     </row>
     <row r="49">
@@ -2423,13 +2423,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.068416</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.068416</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.03445</v>
       </c>
     </row>
     <row r="125">
@@ -2439,13 +2439,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.068416</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.068416</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.03445</v>
       </c>
     </row>
     <row r="126">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -4139,7 +4139,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
         <v>-0.068416</v>
       </c>

--- a/output/pdf_financials_xlsx/JBR.xlsx
+++ b/output/pdf_financials_xlsx/JBR.xlsx
@@ -3808,7 +3808,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -4228,7 +4232,11 @@
           <t>Proceeds from private placement (Note 11)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
